--- a/livrables/marges_par_intergare.xlsx
+++ b/livrables/marges_par_intergare.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="marges_par_intergare" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'marges_par_intergare'!$A$1:$P$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'marges_par_intergare'!$A$1:$S$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -444,8 +444,11 @@
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="46" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="33" customWidth="1" min="18" max="18"/>
+    <col width="46" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -521,10 +524,25 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>dispersion_iqr_min</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dispersion_iqr_pct</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>doublon_physique_de</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>exclue_du_2x2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -581,7 +599,13 @@
       <c r="N2" t="n">
         <v>157.4</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>bloc urbain (pont Victoria)</t>
         </is>
@@ -638,7 +662,13 @@
       <c r="N3" t="n">
         <v>16.5</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>adjacente au pont Victoria</t>
         </is>
@@ -695,6 +725,12 @@
       <c r="N4" t="n">
         <v>26.8</v>
       </c>
+      <c r="O4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>26.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -747,6 +783,12 @@
       <c r="N5" t="n">
         <v>25.3</v>
       </c>
+      <c r="O5" t="n">
+        <v>16</v>
+      </c>
+      <c r="P5" t="n">
+        <v>16.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -799,7 +841,13 @@
       <c r="N6" t="n">
         <v>69.8</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>adjacente au pont de Québec</t>
         </is>
@@ -856,7 +904,13 @@
       <c r="N7" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>bloc urbain (pont de Québec)</t>
         </is>
@@ -913,7 +967,13 @@
       <c r="N8" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>bloc urbain</t>
         </is>
@@ -970,6 +1030,12 @@
       <c r="N9" t="n">
         <v>13.9</v>
       </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>8.699999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1022,6 +1088,12 @@
       <c r="N10" t="n">
         <v>14.1</v>
       </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1074,6 +1146,12 @@
       <c r="N11" t="n">
         <v>10.3</v>
       </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1126,7 +1204,13 @@
       <c r="N12" t="n">
         <v>16.5</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="O12" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>contient l'approche d'Ottawa (±10 km urbains)</t>
         </is>
@@ -1145,17 +1229,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Smiths Falls</t>
+          <t>Fallowfield</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>64.62</v>
+        <v>15.38</v>
       </c>
       <c r="F13" t="n">
-        <v>64.59999999999999</v>
+        <v>15.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1163,29 +1247,35 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="L13" t="n">
-        <v>25.1</v>
+        <v>6.6</v>
       </c>
       <c r="M13" t="n">
-        <v>91.40000000000001</v>
+        <v>158.4</v>
       </c>
       <c r="N13" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>contient l'approche d'Ottawa (±10 km urbains)</t>
+        <v>67.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>bloc urbain (approche d'Ottawa)</t>
         </is>
       </c>
     </row>
@@ -1197,22 +1287,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Fallowfield</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Smiths Falls</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Brockville</t>
-        </is>
-      </c>
       <c r="D14" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="E14" t="n">
         <v>64.62</v>
       </c>
-      <c r="E14" t="n">
-        <v>110</v>
-      </c>
       <c r="F14" t="n">
-        <v>45.4</v>
+        <v>49.2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1226,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K14" t="n">
         <v>11</v>
@@ -1235,10 +1325,16 @@
         <v>18.5</v>
       </c>
       <c r="M14" t="n">
-        <v>62.5</v>
+        <v>51.4</v>
       </c>
       <c r="N14" t="n">
-        <v>25.4</v>
+        <v>19.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>14.3</v>
       </c>
     </row>
     <row r="15">
@@ -1249,48 +1345,54 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>Smiths Falls</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Brockville</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Gananoque</t>
-        </is>
-      </c>
       <c r="D15" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="E15" t="n">
         <v>110</v>
       </c>
-      <c r="E15" t="n">
-        <v>155.83</v>
-      </c>
       <c r="F15" t="n">
-        <v>45.8</v>
+        <v>45.4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>double-CN</t>
+          <t>simple-VIA</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>25.5</v>
+        <v>30</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>17.7</v>
+        <v>18.5</v>
       </c>
       <c r="M15" t="n">
-        <v>44.4</v>
+        <v>62.5</v>
       </c>
       <c r="N15" t="n">
-        <v>17.1</v>
+        <v>25.4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -1301,22 +1403,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Brockville</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Gananoque</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Kingston</t>
-        </is>
-      </c>
       <c r="D16" t="n">
+        <v>110</v>
+      </c>
+      <c r="E16" t="n">
         <v>155.83</v>
       </c>
-      <c r="E16" t="n">
-        <v>191.99</v>
-      </c>
       <c r="F16" t="n">
-        <v>36.2</v>
+        <v>45.8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1324,25 +1426,31 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J16" t="n">
-        <v>20.5</v>
+        <v>25.5</v>
       </c>
       <c r="K16" t="n">
         <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>14.6</v>
+        <v>17.7</v>
       </c>
       <c r="M16" t="n">
-        <v>40.2</v>
+        <v>44.4</v>
       </c>
       <c r="N16" t="n">
-        <v>16.2</v>
+        <v>17.1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="17">
@@ -1353,22 +1461,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Gananoque</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Kingston</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Napanee</t>
-        </is>
-      </c>
       <c r="D17" t="n">
+        <v>155.83</v>
+      </c>
+      <c r="E17" t="n">
         <v>191.99</v>
       </c>
-      <c r="E17" t="n">
-        <v>227.49</v>
-      </c>
       <c r="F17" t="n">
-        <v>35.5</v>
+        <v>36.2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1382,19 +1490,25 @@
         <v>100</v>
       </c>
       <c r="J17" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="M17" t="n">
-        <v>44.3</v>
+        <v>40.2</v>
       </c>
       <c r="N17" t="n">
-        <v>17.3</v>
+        <v>16.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1405,22 +1519,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Kingston</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Napanee</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Belleville</t>
-        </is>
-      </c>
       <c r="D18" t="n">
+        <v>191.99</v>
+      </c>
+      <c r="E18" t="n">
         <v>227.49</v>
       </c>
-      <c r="E18" t="n">
-        <v>262.44</v>
-      </c>
       <c r="F18" t="n">
-        <v>34.9</v>
+        <v>35.5</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1434,19 +1548,25 @@
         <v>100</v>
       </c>
       <c r="J18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K18" t="n">
         <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="M18" t="n">
-        <v>36.3</v>
+        <v>44.3</v>
       </c>
       <c r="N18" t="n">
-        <v>13.7</v>
+        <v>17.3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1457,22 +1577,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>Napanee</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Belleville</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Trenton Junction</t>
-        </is>
-      </c>
       <c r="D19" t="n">
+        <v>227.49</v>
+      </c>
+      <c r="E19" t="n">
         <v>262.44</v>
       </c>
-      <c r="E19" t="n">
-        <v>281.92</v>
-      </c>
       <c r="F19" t="n">
-        <v>19.5</v>
+        <v>34.9</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1486,19 +1606,25 @@
         <v>100</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>7.3</v>
+        <v>13.2</v>
       </c>
       <c r="M19" t="n">
-        <v>65.09999999999999</v>
+        <v>36.3</v>
       </c>
       <c r="N19" t="n">
-        <v>24.3</v>
+        <v>13.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1509,22 +1635,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>Belleville</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Trenton Junction</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Cobourg</t>
-        </is>
-      </c>
       <c r="D20" t="n">
+        <v>262.44</v>
+      </c>
+      <c r="E20" t="n">
         <v>281.92</v>
       </c>
-      <c r="E20" t="n">
-        <v>332.06</v>
-      </c>
       <c r="F20" t="n">
-        <v>50.1</v>
+        <v>19.5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1538,19 +1664,25 @@
         <v>100</v>
       </c>
       <c r="J20" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
         <v>7</v>
       </c>
       <c r="L20" t="n">
-        <v>18.7</v>
+        <v>7.3</v>
       </c>
       <c r="M20" t="n">
-        <v>33.6</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>12.5</v>
+        <v>24.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1561,22 +1693,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Trenton Junction</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Cobourg</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Port Hope</t>
-        </is>
-      </c>
       <c r="D21" t="n">
+        <v>281.92</v>
+      </c>
+      <c r="E21" t="n">
         <v>332.06</v>
       </c>
-      <c r="E21" t="n">
-        <v>342.88</v>
-      </c>
       <c r="F21" t="n">
-        <v>10.8</v>
+        <v>50.1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1590,19 +1722,25 @@
         <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L21" t="n">
-        <v>4.7</v>
+        <v>18.7</v>
       </c>
       <c r="M21" t="n">
-        <v>69.8</v>
+        <v>33.6</v>
       </c>
       <c r="N21" t="n">
-        <v>30.4</v>
+        <v>12.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1613,22 +1751,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Cobourg</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Port Hope</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Oshawa</t>
-        </is>
-      </c>
       <c r="D22" t="n">
+        <v>332.06</v>
+      </c>
+      <c r="E22" t="n">
         <v>342.88</v>
       </c>
-      <c r="E22" t="n">
-        <v>393.31</v>
-      </c>
       <c r="F22" t="n">
-        <v>50.4</v>
+        <v>10.8</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1642,19 +1780,25 @@
         <v>100</v>
       </c>
       <c r="J22" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>19.6</v>
+        <v>4.7</v>
       </c>
       <c r="M22" t="n">
-        <v>32.8</v>
+        <v>69.8</v>
       </c>
       <c r="N22" t="n">
-        <v>12.7</v>
+        <v>30.4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="23">
@@ -1665,22 +1809,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>Port Hope</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Oshawa</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Guildwood</t>
-        </is>
-      </c>
       <c r="D23" t="n">
+        <v>342.88</v>
+      </c>
+      <c r="E23" t="n">
         <v>393.31</v>
       </c>
-      <c r="E23" t="n">
-        <v>423.93</v>
-      </c>
       <c r="F23" t="n">
-        <v>30.6</v>
+        <v>50.4</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1688,25 +1832,31 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J23" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K23" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>11.4</v>
+        <v>19.6</v>
       </c>
       <c r="M23" t="n">
-        <v>49.6</v>
+        <v>32.8</v>
       </c>
       <c r="N23" t="n">
-        <v>18.4</v>
+        <v>12.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="24">
@@ -1717,22 +1867,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Oshawa</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Guildwood</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Toronto</t>
-        </is>
-      </c>
       <c r="D24" t="n">
+        <v>393.31</v>
+      </c>
+      <c r="E24" t="n">
         <v>423.93</v>
       </c>
-      <c r="E24" t="n">
-        <v>444.05</v>
-      </c>
       <c r="F24" t="n">
-        <v>20.1</v>
+        <v>30.6</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1740,56 +1890,57 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L24" t="n">
-        <v>8.1</v>
+        <v>11.4</v>
       </c>
       <c r="M24" t="n">
-        <v>123.2</v>
+        <v>49.6</v>
       </c>
       <c r="N24" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>bloc urbain</t>
-        </is>
+        <v>18.4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>8</v>
+      </c>
+      <c r="P24" t="n">
+        <v>47.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Montréal</t>
+          <t>Guildwood</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dorval</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>423.93</v>
       </c>
       <c r="E25" t="n">
-        <v>17.79</v>
+        <v>444.05</v>
       </c>
       <c r="F25" t="n">
-        <v>17.8</v>
+        <v>20.1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1797,27 +1948,33 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="J25" t="n">
-        <v>23.5</v>
+        <v>18</v>
       </c>
       <c r="K25" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="L25" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="M25" t="n">
-        <v>176.7</v>
+        <v>123.2</v>
       </c>
       <c r="N25" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="O25" t="inlineStr">
+        <v>49.4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>bloc urbain</t>
         </is>
@@ -1831,22 +1988,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>Dorval</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Brockville</t>
-        </is>
-      </c>
       <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
         <v>17.79</v>
       </c>
-      <c r="E26" t="n">
-        <v>204.72</v>
-      </c>
       <c r="F26" t="n">
-        <v>186.9</v>
+        <v>17.8</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1854,25 +2011,41 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I26" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="J26" t="n">
-        <v>96.5</v>
+        <v>23.5</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="L26" t="n">
-        <v>70</v>
+        <v>8.5</v>
       </c>
       <c r="M26" t="n">
-        <v>37.9</v>
+        <v>176.7</v>
       </c>
       <c r="N26" t="n">
-        <v>14.2</v>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>MTL-Ott</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>bloc urbain</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1883,22 +2056,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Brockville</t>
+          <t>Dorval</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gananoque</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>204.72</v>
+        <v>17.79</v>
       </c>
       <c r="E27" t="n">
-        <v>249.75</v>
+        <v>112.76</v>
       </c>
       <c r="F27" t="n">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1912,19 +2085,25 @@
         <v>100</v>
       </c>
       <c r="J27" t="n">
-        <v>25.5</v>
+        <v>48</v>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L27" t="n">
-        <v>17</v>
+        <v>35.6</v>
       </c>
       <c r="M27" t="n">
-        <v>49.7</v>
+        <v>34.9</v>
       </c>
       <c r="N27" t="n">
-        <v>18.8</v>
+        <v>13.1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2</v>
+      </c>
+      <c r="P27" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="28">
@@ -1935,22 +2114,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gananoque</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Brockville</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>249.75</v>
+        <v>112.76</v>
       </c>
       <c r="E28" t="n">
-        <v>285.97</v>
+        <v>204.72</v>
       </c>
       <c r="F28" t="n">
-        <v>36.2</v>
+        <v>92</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1964,19 +2143,25 @@
         <v>100</v>
       </c>
       <c r="J28" t="n">
-        <v>20.5</v>
+        <v>45.5</v>
       </c>
       <c r="K28" t="n">
         <v>4</v>
       </c>
       <c r="L28" t="n">
-        <v>14.9</v>
+        <v>34.4</v>
       </c>
       <c r="M28" t="n">
-        <v>37.4</v>
+        <v>32.3</v>
       </c>
       <c r="N28" t="n">
-        <v>15.4</v>
+        <v>12.1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2</v>
+      </c>
+      <c r="P28" t="n">
+        <v>4.4</v>
       </c>
     </row>
     <row r="29">
@@ -1987,22 +2172,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Brockville</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Napanee</t>
+          <t>Gananoque</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>285.97</v>
+        <v>204.72</v>
       </c>
       <c r="E29" t="n">
-        <v>321.47</v>
+        <v>249.75</v>
       </c>
       <c r="F29" t="n">
-        <v>35.5</v>
+        <v>45</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2016,19 +2201,30 @@
         <v>100</v>
       </c>
       <c r="J29" t="n">
-        <v>20</v>
+        <v>25.5</v>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L29" t="n">
-        <v>13.8</v>
+        <v>17</v>
       </c>
       <c r="M29" t="n">
-        <v>44.7</v>
+        <v>49.7</v>
       </c>
       <c r="N29" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2039,22 +2235,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Napanee</t>
+          <t>Gananoque</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belleville</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>321.47</v>
+        <v>249.75</v>
       </c>
       <c r="E30" t="n">
-        <v>356.42</v>
+        <v>285.97</v>
       </c>
       <c r="F30" t="n">
-        <v>34.9</v>
+        <v>36.2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2068,19 +2264,30 @@
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>18</v>
+        <v>20.5</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L30" t="n">
-        <v>13.2</v>
+        <v>14.9</v>
       </c>
       <c r="M30" t="n">
-        <v>36.1</v>
+        <v>37.4</v>
       </c>
       <c r="N30" t="n">
-        <v>13.7</v>
+        <v>15.4</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2091,22 +2298,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Belleville</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Trenton Junction</t>
+          <t>Napanee</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>356.42</v>
+        <v>285.97</v>
       </c>
       <c r="E31" t="n">
-        <v>375.9</v>
+        <v>321.47</v>
       </c>
       <c r="F31" t="n">
-        <v>19.5</v>
+        <v>35.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2120,19 +2327,30 @@
         <v>100</v>
       </c>
       <c r="J31" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
-        <v>7.3</v>
+        <v>13.8</v>
       </c>
       <c r="M31" t="n">
-        <v>65.09999999999999</v>
+        <v>44.7</v>
       </c>
       <c r="N31" t="n">
-        <v>24.3</v>
+        <v>17.4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2143,22 +2361,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trenton Junction</t>
+          <t>Napanee</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cobourg</t>
+          <t>Belleville</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>375.9</v>
+        <v>321.47</v>
       </c>
       <c r="E32" t="n">
-        <v>426.05</v>
+        <v>356.42</v>
       </c>
       <c r="F32" t="n">
-        <v>50.2</v>
+        <v>34.9</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2172,19 +2390,30 @@
         <v>100</v>
       </c>
       <c r="J32" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L32" t="n">
-        <v>18.7</v>
+        <v>13.2</v>
       </c>
       <c r="M32" t="n">
-        <v>33.5</v>
+        <v>36.1</v>
       </c>
       <c r="N32" t="n">
-        <v>12.5</v>
+        <v>13.7</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -2195,22 +2424,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cobourg</t>
+          <t>Belleville</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Port Hope</t>
+          <t>Trenton Junction</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>426.05</v>
+        <v>356.42</v>
       </c>
       <c r="E33" t="n">
-        <v>436.86</v>
+        <v>375.9</v>
       </c>
       <c r="F33" t="n">
-        <v>10.8</v>
+        <v>19.5</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2224,19 +2453,30 @@
         <v>100</v>
       </c>
       <c r="J33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L33" t="n">
-        <v>4.6</v>
+        <v>7.3</v>
       </c>
       <c r="M33" t="n">
-        <v>72.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>31.2</v>
+        <v>24.3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2247,22 +2487,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Port Hope</t>
+          <t>Trenton Junction</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oshawa</t>
+          <t>Cobourg</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>436.86</v>
+        <v>375.9</v>
       </c>
       <c r="E34" t="n">
-        <v>487.24</v>
+        <v>426.05</v>
       </c>
       <c r="F34" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2276,19 +2516,30 @@
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L34" t="n">
-        <v>19.6</v>
+        <v>18.7</v>
       </c>
       <c r="M34" t="n">
-        <v>32.4</v>
+        <v>33.5</v>
       </c>
       <c r="N34" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2299,22 +2550,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Oshawa</t>
+          <t>Cobourg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Guildwood</t>
+          <t>Port Hope</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>487.24</v>
+        <v>426.05</v>
       </c>
       <c r="E35" t="n">
-        <v>517.9400000000001</v>
+        <v>436.86</v>
       </c>
       <c r="F35" t="n">
-        <v>30.7</v>
+        <v>10.8</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2322,25 +2573,36 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J35" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="K35" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L35" t="n">
-        <v>11.4</v>
+        <v>4.6</v>
       </c>
       <c r="M35" t="n">
-        <v>49.2</v>
+        <v>72.7</v>
       </c>
       <c r="N35" t="n">
-        <v>18.3</v>
+        <v>31.2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -2351,57 +2613,194 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>Port Hope</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Oshawa</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>436.86</v>
+      </c>
+      <c r="E36" t="n">
+        <v>487.24</v>
+      </c>
+      <c r="F36" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>100</v>
+      </c>
+      <c r="J36" t="n">
+        <v>26</v>
+      </c>
+      <c r="K36" t="n">
+        <v>5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="M36" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="N36" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Oshawa</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>Guildwood</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D37" t="n">
+        <v>487.24</v>
+      </c>
+      <c r="E37" t="n">
+        <v>517.9400000000001</v>
+      </c>
+      <c r="F37" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>98</v>
+      </c>
+      <c r="J37" t="n">
+        <v>17</v>
+      </c>
+      <c r="K37" t="n">
+        <v>16</v>
+      </c>
+      <c r="L37" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="M37" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="N37" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="O37" t="n">
+        <v>8</v>
+      </c>
+      <c r="P37" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Guildwood</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>Toronto</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D38" t="n">
         <v>517.9400000000001</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E38" t="n">
         <v>538.0599999999999</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F38" t="n">
         <v>20.1</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="H38" t="n">
         <v>4</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I38" t="n">
         <v>96</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J38" t="n">
         <v>18</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K38" t="n">
         <v>17</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L38" t="n">
         <v>7.9</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M38" t="n">
         <v>127.6</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N38" t="n">
         <v>50.2</v>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>bloc urbain</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P36"/>
+  <autoFilter ref="A1:S38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/livrables/marges_par_intergare.xlsx
+++ b/livrables/marges_par_intergare.xlsx
@@ -447,7 +447,7 @@
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
-    <col width="33" customWidth="1" min="18" max="18"/>
+    <col width="41" customWidth="1" min="18" max="18"/>
     <col width="46" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -1916,6 +1916,11 @@
       <c r="P24" t="n">
         <v>47.1</v>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>chevauche une frontière de propriétaire</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1944,7 +1949,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>double-CN</t>
+          <t>double-MTX</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -2730,6 +2735,11 @@
           <t>Ott-TO</t>
         </is>
       </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>chevauche une frontière de propriétaire</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2758,7 +2768,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>double-CN</t>
+          <t>double-MTX</t>
         </is>
       </c>
       <c r="H38" t="n">

--- a/livrables/marges_par_intergare.xlsx
+++ b/livrables/marges_par_intergare.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="marges_par_intergare" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'marges_par_intergare'!$A$1:$S$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'marges_par_intergare'!$A$1:$T$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,28 +427,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:T57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="21" customWidth="1" min="17" max="17"/>
-    <col width="41" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
     <col width="46" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,90 +460,95 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>de</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>km_debut</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>km_fin</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>longueur_km</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>cellule</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>part_simple_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>part_double_plus_pct</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>t_horaire_med_min</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>n_sillons</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>t_base_S1cap160_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>marge_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>marge_min_par_100km</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dispersion_iqr_min</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dispersion_iqr_pct</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>doublon_physique_de</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>exclue_du_2x2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -556,56 +562,61 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Saint-Lambert</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>6.11</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>6.1</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>16</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>84</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>13</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>16</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>3.4</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>284.1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>157.4</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>bloc urbain (pont Victoria)</t>
         </is>
@@ -619,56 +630,61 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Saint-Lambert</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Saint-Hyacinthe</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>6.11</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>53.24</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>47.1</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>100</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>26</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>14</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>18.2</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>42.7</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>16.5</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>3.8</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>adjacente au pont Victoria</t>
         </is>
@@ -682,53 +698,58 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Saint-Hyacinthe</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Drummondville</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>53.24</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>100.01</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>46.8</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>simple-CN</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>92</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>30.5</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>14</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>18</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>26.8</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>8</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>26.2</v>
       </c>
     </row>
@@ -740,53 +761,58 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Drummondville</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Charny</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>100.01</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>245.04</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>145</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>simple-CN</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>100</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>97</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>7</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>60.3</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>60.8</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>25.3</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>16</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>16.5</v>
       </c>
     </row>
@@ -798,56 +824,61 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Charny</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Sainte-Foy</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>245.04</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>249.98</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>4.9</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>simple-CN</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>100</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>6</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>7</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>2.6</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>135.1</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>69.8</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>adjacente au pont de Québec</t>
         </is>
@@ -861,56 +892,61 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Sainte-Foy</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>249.98</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>269.85</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>19.9</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>mixte</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>65</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>35</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>25</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>14</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>10.9</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>130.1</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>bloc urbain (pont de Québec)</t>
         </is>
@@ -924,56 +960,61 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Dorval</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>17.79</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>17.8</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>21</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>79</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>23.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>26</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>8.5</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>177</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>2</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>8.5</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>bloc urbain</t>
         </is>
@@ -987,53 +1028,58 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Dorval</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Coteau</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>17.79</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>62.28</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>44.5</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>100</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>23</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>7</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>16.8</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>36.8</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>13.9</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>8.699999999999999</v>
       </c>
     </row>
@@ -1045,53 +1091,58 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Coteau</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Alexandria</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>62.28</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>99.43000000000001</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>37.2</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>simple-VIA</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>98</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>21</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>7</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>15.8</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>33.2</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>14.1</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1103,53 +1154,58 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Alexandria</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Casselman</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>99.43000000000001</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>138.78</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>39.3</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>simple-VIA</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>100</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>21</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>16.9</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>24</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>10.3</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1161,56 +1217,61 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Casselman</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>138.78</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>185.42</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>46.6</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>simple-VIA</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>100</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>26</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>7</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>18.3</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>42</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>16.5</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>5</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>19.2</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>contient l'approche d'Ottawa (±10 km urbains)</t>
         </is>
@@ -1224,56 +1285,61 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Fallowfield</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
       <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>15.38</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>15.4</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>simple-VIA</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>93</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>7</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>17</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>21</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>6.6</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>158.4</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>67.8</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>1</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>5.9</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>bloc urbain (approche d'Ottawa)</t>
         </is>
@@ -1287,53 +1353,58 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Fallowfield</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Smiths Falls</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>15.38</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>64.62</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>49.2</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>simple-VIA</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>100</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>28</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>11</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>18.5</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>51.4</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>19.3</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>4</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>14.3</v>
       </c>
     </row>
@@ -1345,53 +1416,58 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Smiths Falls</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Brockville</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>64.62</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>110</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>45.4</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>simple-VIA</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>100</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>30</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>11</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>18.5</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>62.5</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>25.4</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>3</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1403,53 +1479,58 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Brockville</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Gananoque</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>110</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>155.83</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>45.8</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>98</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>25.5</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>4</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>17.7</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>44.4</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>17.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>2</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>7.8</v>
       </c>
     </row>
@@ -1461,53 +1542,58 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Gananoque</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Kingston</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>155.83</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>191.99</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>36.2</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>100</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>20.5</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>14.6</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>40.2</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>16.2</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>2</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>9.800000000000001</v>
       </c>
     </row>
@@ -1519,53 +1605,58 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Kingston</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Napanee</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>191.99</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>227.49</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>35.5</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
       <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>100</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>20</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>6</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>13.9</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>44.3</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>17.3</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>1</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1577,53 +1668,58 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Napanee</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Belleville</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>227.49</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>262.44</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>34.9</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
       <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>100</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>18</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>6</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>13.2</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>36.3</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>13.7</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1635,53 +1731,58 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Belleville</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Trenton Junction</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>262.44</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>281.92</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>19.5</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
       <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
         <v>100</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>12</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>7</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>7.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>24.3</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>1</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>8.300000000000001</v>
       </c>
     </row>
@@ -1693,53 +1794,58 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Trenton Junction</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Cobourg</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>281.92</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>332.06</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>50.1</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>100</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>25</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>7</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>18.7</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>33.6</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>12.5</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>1</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1751,53 +1857,58 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Cobourg</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Port Hope</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>332.06</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>342.88</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>10.8</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
       <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
         <v>100</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>8</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>6</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>4.7</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>69.8</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>30.4</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>1</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -1809,53 +1920,58 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Port Hope</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Oshawa</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>342.88</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>393.31</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>50.4</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
       <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>100</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>26</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>5</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>19.6</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>32.8</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>12.7</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>1</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -1867,58 +1983,63 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Oshawa</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Guildwood</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>393.31</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>423.93</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>30.6</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>2</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>98</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>17</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>16</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>11.4</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>49.6</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>18.4</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>8</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>47.1</v>
       </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>chevauche une frontière de propriétaire</t>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>chevauche une frontière de propriétaire (CN 68%)</t>
         </is>
       </c>
     </row>
@@ -1930,56 +2051,61 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Guildwood</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Toronto</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>423.93</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>444.05</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>20.1</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>double-MTX</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>4</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>96</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>18</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>17</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>8.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>123.2</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>49.4</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>5.6</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>bloc urbain</t>
         </is>
@@ -1988,829 +2114,2051 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>TO-WDN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Montréal</t>
+          <t>sud-ouest</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dorval</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Oakville</t>
+        </is>
       </c>
       <c r="E26" t="n">
-        <v>17.79</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>double-CN</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>21</v>
+        <v>34.06</v>
+      </c>
+      <c r="G26" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>double-MTX</t>
+        </is>
       </c>
       <c r="I26" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
+        <v>100</v>
+      </c>
+      <c r="K26" t="n">
         <v>23.5</v>
       </c>
-      <c r="K26" t="n">
-        <v>26</v>
-      </c>
       <c r="L26" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>176.7</v>
+        <v>13.4</v>
       </c>
       <c r="N26" t="n">
-        <v>84.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
+        <v>29.6</v>
       </c>
       <c r="P26" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>MTL-Ott</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>bloc urbain</t>
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>banlieue Toronto (Metrolinx) : cellule indicative</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>TO-WDN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dorval</t>
+          <t>sud-ouest</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cornwall</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>17.79</v>
+          <t>Oakville</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Aldershot</t>
+        </is>
       </c>
       <c r="E27" t="n">
-        <v>112.76</v>
+        <v>34.06</v>
       </c>
       <c r="F27" t="n">
-        <v>95</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>double-CN</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
+        <v>57.09</v>
+      </c>
+      <c r="G27" t="n">
+        <v>23</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>double-MTX</t>
+        </is>
       </c>
       <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>100</v>
       </c>
-      <c r="J27" t="n">
-        <v>48</v>
-      </c>
       <c r="K27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L27" t="n">
-        <v>35.6</v>
+        <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>34.9</v>
+        <v>8.6</v>
       </c>
       <c r="N27" t="n">
-        <v>13.1</v>
+        <v>50.4</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>18.9</v>
       </c>
       <c r="P27" t="n">
-        <v>4.2</v>
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>chevauche une frontière de propriétaire (MTX 70%)</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>TO-WDN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>sud-ouest</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brockville</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>112.76</v>
+          <t>Aldershot</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Brantford</t>
+        </is>
       </c>
       <c r="E28" t="n">
-        <v>204.72</v>
+        <v>57.09</v>
       </c>
       <c r="F28" t="n">
-        <v>92</v>
-      </c>
-      <c r="G28" t="inlineStr">
+        <v>96.23</v>
+      </c>
+      <c r="G28" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>45.5</v>
+        <v>96</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="L28" t="n">
-        <v>34.4</v>
+        <v>9</v>
       </c>
       <c r="M28" t="n">
-        <v>32.3</v>
+        <v>16</v>
       </c>
       <c r="N28" t="n">
-        <v>12.1</v>
+        <v>74.8</v>
       </c>
       <c r="O28" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="P28" t="n">
         <v>2</v>
       </c>
-      <c r="P28" t="n">
-        <v>4.4</v>
+      <c r="Q28" t="n">
+        <v>7.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>TO-WDN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Brockville</t>
+          <t>sud-ouest</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gananoque</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>204.72</v>
+          <t>Brantford</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Woodstock</t>
+        </is>
       </c>
       <c r="E29" t="n">
-        <v>249.75</v>
+        <v>96.23</v>
       </c>
       <c r="F29" t="n">
-        <v>45</v>
-      </c>
-      <c r="G29" t="inlineStr">
+        <v>138.87</v>
+      </c>
+      <c r="G29" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
       <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>100</v>
       </c>
-      <c r="J29" t="n">
-        <v>25.5</v>
-      </c>
       <c r="K29" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="L29" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M29" t="n">
-        <v>49.7</v>
+        <v>16.7</v>
       </c>
       <c r="N29" t="n">
-        <v>18.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="O29" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="P29" t="n">
         <v>2</v>
       </c>
-      <c r="P29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Ott-TO</t>
-        </is>
+      <c r="Q29" t="n">
+        <v>7.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>TO-WDN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gananoque</t>
+          <t>sud-ouest</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kingston</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>249.75</v>
+          <t>Woodstock</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Ingersoll</t>
+        </is>
       </c>
       <c r="E30" t="n">
-        <v>285.97</v>
+        <v>138.87</v>
       </c>
       <c r="F30" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="G30" t="inlineStr">
+        <v>153.96</v>
+      </c>
+      <c r="G30" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
       <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
         <v>100</v>
       </c>
-      <c r="J30" t="n">
-        <v>20.5</v>
-      </c>
       <c r="K30" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L30" t="n">
-        <v>14.9</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>37.4</v>
+        <v>5.6</v>
       </c>
       <c r="N30" t="n">
-        <v>15.4</v>
+        <v>114.1</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>42.4</v>
       </c>
       <c r="P30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Ott-TO</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>TO-WDN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>sud-ouest</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Napanee</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>285.97</v>
+          <t>Ingersoll</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
       </c>
       <c r="E31" t="n">
-        <v>321.47</v>
+        <v>153.96</v>
       </c>
       <c r="F31" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="G31" t="inlineStr">
+        <v>184.49</v>
+      </c>
+      <c r="G31" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
       <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
         <v>100</v>
       </c>
-      <c r="J31" t="n">
-        <v>20</v>
-      </c>
       <c r="K31" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="L31" t="n">
         <v>6</v>
       </c>
-      <c r="L31" t="n">
-        <v>13.8</v>
-      </c>
       <c r="M31" t="n">
-        <v>44.7</v>
+        <v>11.6</v>
       </c>
       <c r="N31" t="n">
-        <v>17.4</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="O31" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="P31" t="n">
         <v>1</v>
       </c>
-      <c r="P31" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Ott-TO</t>
-        </is>
+      <c r="Q31" t="n">
+        <v>4.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>TO-WDN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Napanee</t>
+          <t>sud-ouest</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belleville</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>321.47</v>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Glencoe</t>
+        </is>
       </c>
       <c r="E32" t="n">
-        <v>356.42</v>
+        <v>184.49</v>
       </c>
       <c r="F32" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>double-CN</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
+        <v>233.71</v>
+      </c>
+      <c r="G32" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>mixte</t>
+        </is>
       </c>
       <c r="I32" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="J32" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K32" t="n">
+        <v>30</v>
+      </c>
+      <c r="L32" t="n">
         <v>6</v>
       </c>
-      <c r="L32" t="n">
-        <v>13.2</v>
-      </c>
       <c r="M32" t="n">
-        <v>36.1</v>
+        <v>18.4</v>
       </c>
       <c r="N32" t="n">
-        <v>13.7</v>
+        <v>62.9</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Ott-TO</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>13.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>TO-WDN</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Belleville</t>
+          <t>sud-ouest</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Trenton Junction</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>356.42</v>
+          <t>Glencoe</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Chatham</t>
+        </is>
       </c>
       <c r="E33" t="n">
-        <v>375.9</v>
+        <v>233.71</v>
       </c>
       <c r="F33" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>double-CN</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
+        <v>288.16</v>
+      </c>
+      <c r="G33" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>mixte</t>
+        </is>
       </c>
       <c r="I33" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="J33" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="K33" t="n">
-        <v>7</v>
+        <v>32.5</v>
       </c>
       <c r="L33" t="n">
-        <v>7.3</v>
+        <v>6</v>
       </c>
       <c r="M33" t="n">
-        <v>65.09999999999999</v>
+        <v>20.4</v>
       </c>
       <c r="N33" t="n">
-        <v>24.3</v>
+        <v>59.3</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>22.2</v>
       </c>
       <c r="P33" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Ott-TO</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>6.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>TO-WDN</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Trenton Junction</t>
+          <t>sud-ouest</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cobourg</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>375.9</v>
+          <t>Chatham</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Windsor</t>
+        </is>
       </c>
       <c r="E34" t="n">
-        <v>426.05</v>
+        <v>288.16</v>
       </c>
       <c r="F34" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>double-CN</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
+        <v>358.75</v>
+      </c>
+      <c r="G34" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>simple-VIA</t>
+        </is>
       </c>
       <c r="I34" t="n">
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M34" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="N34" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="O34" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P34" t="n">
         <v>7</v>
       </c>
-      <c r="L34" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M34" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1</v>
-      </c>
-      <c r="P34" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Ott-TO</t>
-        </is>
+      <c r="Q34" t="n">
+        <v>15.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>TO-SAR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cobourg</t>
+          <t>sud-ouest</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Port Hope</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>426.05</v>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Malton</t>
+        </is>
       </c>
       <c r="E35" t="n">
-        <v>436.86</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>double-CN</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
+        <v>25.65</v>
+      </c>
+      <c r="G35" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>double-MTX</t>
+        </is>
       </c>
       <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
         <v>100</v>
       </c>
-      <c r="J35" t="n">
-        <v>8</v>
-      </c>
       <c r="K35" t="n">
-        <v>6</v>
+        <v>22.5</v>
       </c>
       <c r="L35" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>72.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>31.2</v>
+        <v>131.6</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
-      </c>
-      <c r="P35" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Ott-TO</t>
+        <v>49.8</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>banlieue Toronto (Metrolinx) : cellule indicative</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>TO-SAR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Port Hope</t>
+          <t>sud-ouest</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oshawa</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>436.86</v>
+          <t>Malton</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Brampton</t>
+        </is>
       </c>
       <c r="E36" t="n">
-        <v>487.24</v>
+        <v>25.65</v>
       </c>
       <c r="F36" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="G36" t="inlineStr">
+        <v>34.12</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
       <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
         <v>100</v>
       </c>
-      <c r="J36" t="n">
-        <v>26</v>
-      </c>
       <c r="K36" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="L36" t="n">
-        <v>19.6</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>32.4</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>12.6</v>
+        <v>235.7</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
-      </c>
-      <c r="P36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Ott-TO</t>
+        <v>87</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>banlieue Toronto (Metrolinx) : cellule indicative</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>TO-SAR</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Oshawa</t>
+          <t>sud-ouest</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Guildwood</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>487.24</v>
+          <t>Brampton</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Georgetown</t>
+        </is>
       </c>
       <c r="E37" t="n">
-        <v>517.9400000000001</v>
+        <v>34.12</v>
       </c>
       <c r="F37" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="G37" t="inlineStr">
+        <v>47.09</v>
+      </c>
+      <c r="G37" t="n">
+        <v>13</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>double-CN</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>100</v>
+      </c>
+      <c r="K37" t="n">
+        <v>10</v>
+      </c>
+      <c r="L37" t="n">
         <v>2</v>
       </c>
-      <c r="I37" t="n">
-        <v>98</v>
-      </c>
-      <c r="J37" t="n">
-        <v>17</v>
-      </c>
-      <c r="K37" t="n">
-        <v>16</v>
-      </c>
-      <c r="L37" t="n">
-        <v>11.4</v>
-      </c>
       <c r="M37" t="n">
-        <v>49.2</v>
+        <v>4.8</v>
       </c>
       <c r="N37" t="n">
-        <v>18.3</v>
+        <v>107.2</v>
       </c>
       <c r="O37" t="n">
-        <v>8</v>
-      </c>
-      <c r="P37" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Ott-TO</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>chevauche une frontière de propriétaire</t>
-        </is>
+        <v>39.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>TO-SAR</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sud-ouest</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Georgetown</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Guelph</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>47.09</v>
+      </c>
+      <c r="F38" t="n">
+        <v>78.41</v>
+      </c>
+      <c r="G38" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>simple-MTX</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>95</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>22</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>12</v>
+      </c>
+      <c r="N38" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TO-SAR</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>sud-ouest</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Guelph</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Kitchener</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>78.41</v>
+      </c>
+      <c r="F39" t="n">
+        <v>101.06</v>
+      </c>
+      <c r="G39" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>simple-MTX</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>84</v>
+      </c>
+      <c r="J39" t="n">
+        <v>16</v>
+      </c>
+      <c r="K39" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="N39" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TO-SAR</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>sud-ouest</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Kitchener</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Stratford</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>101.06</v>
+      </c>
+      <c r="F40" t="n">
+        <v>142.16</v>
+      </c>
+      <c r="G40" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>simple-CN</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>97</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="N40" t="n">
+        <v>172</v>
+      </c>
+      <c r="O40" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TO-SAR</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>sud-ouest</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Stratford</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>St. Marys</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>142.16</v>
+      </c>
+      <c r="F41" t="n">
+        <v>160.16</v>
+      </c>
+      <c r="G41" t="n">
+        <v>18</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>simple-CN</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>100</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>27</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N41" t="n">
+        <v>259</v>
+      </c>
+      <c r="O41" t="n">
+        <v>108.2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TO-SAR</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>sud-ouest</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>St. Marys</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>160.16</v>
+      </c>
+      <c r="F42" t="n">
+        <v>194.61</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>simple-CN</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>97</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3</v>
+      </c>
+      <c r="K42" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>258.6</v>
+      </c>
+      <c r="O42" t="n">
+        <v>101.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TO-SAR</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>sud-ouest</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Strathroy</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>194.61</v>
+      </c>
+      <c r="F43" t="n">
+        <v>225.4</v>
+      </c>
+      <c r="G43" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>18</v>
+      </c>
+      <c r="J43" t="n">
+        <v>82</v>
+      </c>
+      <c r="K43" t="n">
+        <v>22</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="N43" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="O43" t="n">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TO-SAR</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>sud-ouest</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Strathroy</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sarnia</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>225.4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>289.46</v>
+      </c>
+      <c r="G44" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>mixte</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>63</v>
+      </c>
+      <c r="J44" t="n">
+        <v>37</v>
+      </c>
+      <c r="K44" t="n">
+        <v>45</v>
+      </c>
+      <c r="L44" t="n">
+        <v>2</v>
+      </c>
+      <c r="M44" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="N44" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="O44" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>MTL-TO</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Montréal</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Dorval</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="G45" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>21</v>
+      </c>
+      <c r="J45" t="n">
+        <v>79</v>
+      </c>
+      <c r="K45" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="L45" t="n">
+        <v>26</v>
+      </c>
+      <c r="M45" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N45" t="n">
+        <v>176.7</v>
+      </c>
+      <c r="O45" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>MTL-Ott</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>bloc urbain</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Dorval</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Cornwall</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="F46" t="n">
+        <v>112.76</v>
+      </c>
+      <c r="G46" t="n">
+        <v>95</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>100</v>
+      </c>
+      <c r="K46" t="n">
+        <v>48</v>
+      </c>
+      <c r="L46" t="n">
+        <v>12</v>
+      </c>
+      <c r="M46" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="N46" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="O46" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Cornwall</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Brockville</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>112.76</v>
+      </c>
+      <c r="F47" t="n">
+        <v>204.72</v>
+      </c>
+      <c r="G47" t="n">
+        <v>92</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>100</v>
+      </c>
+      <c r="K47" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="L47" t="n">
+        <v>4</v>
+      </c>
+      <c r="M47" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="N47" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="O47" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Brockville</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Gananoque</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>204.72</v>
+      </c>
+      <c r="F48" t="n">
+        <v>249.75</v>
+      </c>
+      <c r="G48" t="n">
+        <v>45</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>100</v>
+      </c>
+      <c r="K48" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="L48" t="n">
+        <v>4</v>
+      </c>
+      <c r="M48" t="n">
+        <v>17</v>
+      </c>
+      <c r="N48" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="O48" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Gananoque</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Kingston</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>249.75</v>
+      </c>
+      <c r="F49" t="n">
+        <v>285.97</v>
+      </c>
+      <c r="G49" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>100</v>
+      </c>
+      <c r="K49" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="L49" t="n">
+        <v>4</v>
+      </c>
+      <c r="M49" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N49" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="O49" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Kingston</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Napanee</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>285.97</v>
+      </c>
+      <c r="F50" t="n">
+        <v>321.47</v>
+      </c>
+      <c r="G50" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>100</v>
+      </c>
+      <c r="K50" t="n">
+        <v>20</v>
+      </c>
+      <c r="L50" t="n">
+        <v>6</v>
+      </c>
+      <c r="M50" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N50" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="O50" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>5</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Napanee</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Belleville</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>321.47</v>
+      </c>
+      <c r="F51" t="n">
+        <v>356.42</v>
+      </c>
+      <c r="G51" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>100</v>
+      </c>
+      <c r="K51" t="n">
+        <v>18</v>
+      </c>
+      <c r="L51" t="n">
+        <v>6</v>
+      </c>
+      <c r="M51" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="N51" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Belleville</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Trenton Junction</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>356.42</v>
+      </c>
+      <c r="F52" t="n">
+        <v>375.9</v>
+      </c>
+      <c r="G52" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>100</v>
+      </c>
+      <c r="K52" t="n">
+        <v>12</v>
+      </c>
+      <c r="L52" t="n">
+        <v>7</v>
+      </c>
+      <c r="M52" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="N52" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="O52" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Trenton Junction</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Cobourg</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>375.9</v>
+      </c>
+      <c r="F53" t="n">
+        <v>426.05</v>
+      </c>
+      <c r="G53" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>100</v>
+      </c>
+      <c r="K53" t="n">
+        <v>25</v>
+      </c>
+      <c r="L53" t="n">
+        <v>7</v>
+      </c>
+      <c r="M53" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N53" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O53" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>4</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Cobourg</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Port Hope</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>426.05</v>
+      </c>
+      <c r="F54" t="n">
+        <v>436.86</v>
+      </c>
+      <c r="G54" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>100</v>
+      </c>
+      <c r="K54" t="n">
+        <v>8</v>
+      </c>
+      <c r="L54" t="n">
+        <v>6</v>
+      </c>
+      <c r="M54" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N54" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="O54" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Port Hope</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Oshawa</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>436.86</v>
+      </c>
+      <c r="F55" t="n">
+        <v>487.24</v>
+      </c>
+      <c r="G55" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>100</v>
+      </c>
+      <c r="K55" t="n">
+        <v>26</v>
+      </c>
+      <c r="L55" t="n">
+        <v>5</v>
+      </c>
+      <c r="M55" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="N55" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="O55" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Oshawa</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>Guildwood</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="E56" t="n">
+        <v>487.24</v>
+      </c>
+      <c r="F56" t="n">
+        <v>517.9400000000001</v>
+      </c>
+      <c r="G56" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>double-CN</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>98</v>
+      </c>
+      <c r="K56" t="n">
+        <v>17</v>
+      </c>
+      <c r="L56" t="n">
+        <v>16</v>
+      </c>
+      <c r="M56" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N56" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="O56" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="P56" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Ott-TO</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>chevauche une frontière de propriétaire (CN 68%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>coeur</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Guildwood</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>Toronto</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="E57" t="n">
         <v>517.9400000000001</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F57" t="n">
         <v>538.0599999999999</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G57" t="n">
         <v>20.1</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>double-MTX</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="I57" t="n">
         <v>4</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J57" t="n">
         <v>96</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K57" t="n">
         <v>18</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L57" t="n">
         <v>17</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M57" t="n">
         <v>7.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N57" t="n">
         <v>127.6</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O57" t="n">
         <v>50.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P57" t="n">
         <v>1</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q57" t="n">
         <v>5.6</v>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>Ott-TO</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>bloc urbain</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S38"/>
+  <autoFilter ref="A1:T57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>